--- a/Project/outputs/tables/table_gru_metrics_h22.xlsx
+++ b/Project/outputs/tables/table_gru_metrics_h22.xlsx
@@ -482,19 +482,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02625393122434616</v>
+        <v>0.0265522375702858</v>
       </c>
       <c r="C2" t="n">
-        <v>0.08753879368305206</v>
+        <v>0.07549517601728439</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1620306490277261</v>
+        <v>0.1629485733913795</v>
       </c>
       <c r="E2" t="n">
-        <v>52.83056640625</v>
+        <v>39.34624481201172</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4422700587084148</v>
+        <v>0.4755381604696673</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -513,23 +513,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STOXX600</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01282939501106739</v>
+        <v>0.0152604216709733</v>
       </c>
       <c r="C3" t="n">
-        <v>0.06574919074773788</v>
+        <v>0.07124409079551697</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1132669193148087</v>
+        <v>0.1235330792580404</v>
       </c>
       <c r="E3" t="n">
-        <v>45.92844772338867</v>
+        <v>39.45713043212891</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4931506849315068</v>
+        <v>0.4696673189823874</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -548,23 +548,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FTSE100</t>
+          <t>CAC40</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01197938900440931</v>
+        <v>0.01658393442630768</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05988141149282455</v>
+        <v>0.07543215155601501</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1094503951770359</v>
+        <v>0.1287786256577841</v>
       </c>
       <c r="E4" t="n">
-        <v>35.59405899047852</v>
+        <v>42.78322219848633</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4892367906066536</v>
+        <v>0.4951076320939334</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -583,23 +583,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>FTSE100</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01484506204724312</v>
+        <v>0.01216050144284964</v>
       </c>
       <c r="C5" t="n">
-        <v>0.07268640398979187</v>
+        <v>0.05579943582415581</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1218403137194054</v>
+        <v>0.1102746636487713</v>
       </c>
       <c r="E5" t="n">
-        <v>43.07086563110352</v>
+        <v>29.71803283691406</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4853228962818004</v>
+        <v>0.5029354207436399</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -622,19 +622,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.006311805918812752</v>
+        <v>0.007046099752187729</v>
       </c>
       <c r="C6" t="n">
-        <v>0.05890563130378723</v>
+        <v>0.0556708537042141</v>
       </c>
       <c r="D6" t="n">
-        <v>0.07944687482093145</v>
+        <v>0.08394104926785065</v>
       </c>
       <c r="E6" t="n">
-        <v>34.3277587890625</v>
+        <v>31.02598762512207</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4794520547945205</v>
+        <v>0.4911937377690802</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -653,23 +653,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HangSeng</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.006097541190683842</v>
+        <v>0.01505680289119482</v>
       </c>
       <c r="C7" t="n">
-        <v>0.05876738950610161</v>
+        <v>0.06831599026918411</v>
       </c>
       <c r="D7" t="n">
-        <v>0.07808675425886161</v>
+        <v>0.122706164845923</v>
       </c>
       <c r="E7" t="n">
-        <v>31.22358894348145</v>
+        <v>30.21882247924805</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4814090019569471</v>
+        <v>0.5088062622309197</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -688,23 +688,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MSCI_EM</t>
+          <t>HangSeng</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02611508220434189</v>
+        <v>0.006226388271898031</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1125853061676025</v>
+        <v>0.05408303439617157</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1616016157231786</v>
+        <v>0.07890746651552077</v>
       </c>
       <c r="E8" t="n">
-        <v>56.52076721191406</v>
+        <v>25.45407485961914</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4579256360078278</v>
+        <v>0.5048923679060665</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -723,23 +723,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CSI300</t>
+          <t>SSE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.006277751177549362</v>
+        <v>0.007903600111603737</v>
       </c>
       <c r="C9" t="n">
-        <v>0.06302239000797272</v>
+        <v>0.07439905405044556</v>
       </c>
       <c r="D9" t="n">
-        <v>0.07923226096451724</v>
+        <v>0.08890219407643288</v>
       </c>
       <c r="E9" t="n">
-        <v>35.16022109985352</v>
+        <v>53.24032211303711</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4931506849315068</v>
+        <v>0.5088062622309197</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -762,19 +762,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01383874472230673</v>
+        <v>0.01334874826716259</v>
       </c>
       <c r="C10" t="n">
-        <v>0.07239206461235881</v>
+        <v>0.06630497332662344</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1131194728758081</v>
+        <v>0.1124989770827128</v>
       </c>
       <c r="E10" t="n">
-        <v>41.83203506469727</v>
+        <v>36.40547943115234</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4777397260273972</v>
+        <v>0.4946183953033269</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -797,19 +797,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.00483039254322648</v>
+        <v>0.00498595368117094</v>
       </c>
       <c r="C11" t="n">
-        <v>0.04669616743922234</v>
+        <v>0.04401207715272903</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0695010254832724</v>
+        <v>0.07061128579179776</v>
       </c>
       <c r="E11" t="n">
-        <v>30.98159408569336</v>
+        <v>25.68272399902344</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4979480164158687</v>
+        <v>0.5247252747252747</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -828,23 +828,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STOXX600</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.003515623975545168</v>
+        <v>0.003545279148966074</v>
       </c>
       <c r="C12" t="n">
-        <v>0.04460883513092995</v>
+        <v>0.04835595935583115</v>
       </c>
       <c r="D12" t="n">
-        <v>0.05929269748919481</v>
+        <v>0.05954224675779437</v>
       </c>
       <c r="E12" t="n">
-        <v>41.54413223266602</v>
+        <v>37.02674102783203</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5006839945280438</v>
+        <v>0.5233516483516484</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -863,23 +863,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FTSE100</t>
+          <t>CAC40</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.004018994513899088</v>
+        <v>0.002538740169256926</v>
       </c>
       <c r="C13" t="n">
-        <v>0.04962070658802986</v>
+        <v>0.03819814324378967</v>
       </c>
       <c r="D13" t="n">
-        <v>0.06339554017357284</v>
+        <v>0.05038591240869739</v>
       </c>
       <c r="E13" t="n">
-        <v>53.86381149291992</v>
+        <v>28.9308032989502</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4952120383036936</v>
+        <v>0.5096153846153846</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -898,23 +898,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>FTSE100</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.003970685414969921</v>
+        <v>0.002931738970801234</v>
       </c>
       <c r="C14" t="n">
-        <v>0.04906672239303589</v>
+        <v>0.04396406561136246</v>
       </c>
       <c r="D14" t="n">
-        <v>0.06301337488954167</v>
+        <v>0.05414553509571435</v>
       </c>
       <c r="E14" t="n">
-        <v>38.72385787963867</v>
+        <v>47.23014450073242</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5013736263736264</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -937,19 +937,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.01233404036611319</v>
+        <v>0.01247592456638813</v>
       </c>
       <c r="C15" t="n">
-        <v>0.06540568917989731</v>
+        <v>0.07784124463796616</v>
       </c>
       <c r="D15" t="n">
-        <v>0.111058724853625</v>
+        <v>0.1116956783693449</v>
       </c>
       <c r="E15" t="n">
-        <v>32.65496063232422</v>
+        <v>40.45364379882812</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5129958960328317</v>
+        <v>0.5013736263736264</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -968,23 +968,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HangSeng</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.00816604308784008</v>
+        <v>0.006585974246263504</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05994763970375061</v>
+        <v>0.05462382733821869</v>
       </c>
       <c r="D16" t="n">
-        <v>0.09036616118791414</v>
+        <v>0.08115401558927016</v>
       </c>
       <c r="E16" t="n">
-        <v>23.90252876281738</v>
+        <v>27.60713958740234</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5170998632010944</v>
+        <v>0.5247252747252747</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1003,23 +1003,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MSCI_EM</t>
+          <t>HangSeng</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.0112000610679388</v>
+        <v>0.01186117716133595</v>
       </c>
       <c r="C17" t="n">
-        <v>0.08779623359441757</v>
+        <v>0.07970190793275833</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1058303409610817</v>
+        <v>0.1089090315875407</v>
       </c>
       <c r="E17" t="n">
-        <v>60.40474700927734</v>
+        <v>31.17734527587891</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4623803009575924</v>
+        <v>0.5302197802197802</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1038,23 +1038,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CSI300</t>
+          <t>SSE</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.007418610155582428</v>
+        <v>0.008470783941447735</v>
       </c>
       <c r="C18" t="n">
-        <v>0.07400703430175781</v>
+        <v>0.07712378352880478</v>
       </c>
       <c r="D18" t="n">
-        <v>0.08613135407958258</v>
+        <v>0.09203686186223287</v>
       </c>
       <c r="E18" t="n">
-        <v>57.49570083618164</v>
+        <v>67.483154296875</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5075239398084815</v>
+        <v>0.4835164835164835</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1077,19 +1077,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.006931806390639395</v>
+        <v>0.006674446485703811</v>
       </c>
       <c r="C19" t="n">
-        <v>0.05964362854138017</v>
+        <v>0.05797762610018253</v>
       </c>
       <c r="D19" t="n">
-        <v>0.08107365238972315</v>
+        <v>0.07856007093279906</v>
       </c>
       <c r="E19" t="n">
-        <v>42.44641876220703</v>
+        <v>38.1989631652832</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5035909712722298</v>
+        <v>0.5123626373626373</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
